--- a/louvers/files/reference_xls/price_xls/rectangular_30_60.xlsx
+++ b/louvers/files/reference_xls/price_xls/rectangular_30_60.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/snigdhagoel/Documents/Vibrant Technik/vibrant-technik/offer-generator-test/files/reference_xls/price_xls/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/snigdhagoel/Documents/Vibrant Technik/vibrant-technik/offer-generator-test/louvers/files/reference_xls/price_xls/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6234A761-E25F-4648-B7A8-9F057539DB63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5398B653-E624-E045-999E-4F7C5EA15DA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="15940" xr2:uid="{C496E742-E4DE-5F45-8BA5-297BA30B28EC}"/>
   </bookViews>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="D2" s="24">
         <f>+A7*'Per m weight'!B3</f>
-        <v>562.5</v>
+        <v>618.75</v>
       </c>
       <c r="E2" s="31" t="e">
         <f>F2/10.76391</f>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="G2" s="33">
         <f>+D2+((('Per m weight'!C3/25.4)*39.3701)*0.4)</f>
-        <v>674.10028346456693</v>
+        <v>730.35028346456693</v>
       </c>
       <c r="H2" s="40" t="e">
         <f>I2/10.76391</f>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="D3" s="27">
         <f>+A7*'Per m weight'!B4</f>
-        <v>195</v>
+        <v>214.5</v>
       </c>
       <c r="E3" s="34" t="e">
         <f>F3/10.76391</f>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="G3" s="36">
         <f>+D3+((('Per m weight'!C4/25.4)*39.3701)*0.4)</f>
-        <v>233.75009842519685</v>
+        <v>253.25009842519685</v>
       </c>
       <c r="H3" s="43" t="e">
         <f>I3/10.76391</f>
@@ -1127,7 +1127,7 @@
     </row>
     <row r="7" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
-        <v>750</v>
+        <v>825</v>
       </c>
       <c r="B7" s="9"/>
     </row>
